--- a/measurements/26/Filled_2D_sections/coronal/week26_coronal_Batch_Allmarks.xlsx
+++ b/measurements/26/Filled_2D_sections/coronal/week26_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,72 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +566,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.954788816180845</v>
+        <v>1888.662131519274</v>
       </c>
       <c r="D2" t="n">
-        <v>12.33141153033187</v>
+        <v>240.7561298779079</v>
       </c>
       <c r="E2" t="n">
-        <v>9.817903690221833</v>
+        <v>191.6828815709977</v>
       </c>
       <c r="F2" t="n">
         <v>1.256012680447596</v>
@@ -525,24 +585,54 @@
         <v>0.4094580649434686</v>
       </c>
       <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.491815476190476</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.56808035714286</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.38578869047619</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11.56808035714286</v>
+      </c>
+      <c r="N2" t="n">
+        <v>9.4921875</v>
+      </c>
+      <c r="O2" t="n">
+        <v>9.477306547619047</v>
+      </c>
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.5925114329268293</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.5925114329268293</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.5925114329268293</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.5234375</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.491815476190476</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>4.956632956573468</v>
+      <c r="AA2" s="2" t="n">
+        <v>1889.365079365079</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +643,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.967578822129685</v>
+        <v>1893.537414965986</v>
       </c>
       <c r="D3" t="n">
-        <v>12.43489058715541</v>
+        <v>242.7764352730342</v>
       </c>
       <c r="E3" t="n">
-        <v>9.823821756897903</v>
+        <v>191.7984247775305</v>
       </c>
       <c r="F3" t="n">
-        <v>1.265789516022531</v>
+        <v>1.265789516022532</v>
       </c>
       <c r="G3" t="n">
         <v>0.403711103559776</v>
       </c>
       <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.380208333333333</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11.09747023809524</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.373387896825396</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11.09747023809524</v>
+      </c>
+      <c r="N3" t="n">
+        <v>9.494047619047619</v>
+      </c>
+      <c r="O3" t="n">
+        <v>9.45126488095238</v>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.568407012195122</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.568407012195122</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.568407012195122</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="n">
+        <v>5.026041666666666</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.791294642857143</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.380208333333333</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>11.73198595352289</v>
+      <c r="AA3" s="2" t="n">
+        <v>229.0530590925898</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +720,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.996133254015467</v>
+        <v>1904.421768707483</v>
       </c>
       <c r="D4" t="n">
-        <v>12.39447952189097</v>
+        <v>241.9874573321569</v>
       </c>
       <c r="E4" t="n">
-        <v>9.803616227173224</v>
+        <v>191.4039358638582</v>
       </c>
       <c r="F4" t="n">
         <v>1.264276286900797</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4086836736456985</v>
+        <v>0.4086836736456986</v>
       </c>
       <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.495535714285714</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10.62872023809524</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.205977182539683</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10.62872023809524</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9.477306547619047</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9.430803571428571</v>
+      </c>
+      <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.5443978658536586</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.5443978658536586</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.5443978658536586</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="n">
+        <v>4.581473214285714</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.62202380952381</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.495535714285714</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>9.877784911743024</v>
+      <c r="AA4" s="2" t="n">
+        <v>192.8519911340305</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +797,72 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.008328375966687</v>
+        <v>1909.07029478458</v>
       </c>
       <c r="D5" t="n">
-        <v>12.39693085740252</v>
+        <v>242.0353167397635</v>
       </c>
       <c r="E5" t="n">
-        <v>9.83810923448423</v>
+        <v>192.0773707685016</v>
       </c>
       <c r="F5" t="n">
         <v>1.260092824945386</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4095192320609583</v>
+        <v>0.4095192320609582</v>
       </c>
       <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.320684523809524</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10.76822916666667</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.167844742063491</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10.76822916666667</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9.454985119047619</v>
+      </c>
+      <c r="O5" t="n">
+        <v>9.205729166666666</v>
+      </c>
+      <c r="P5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.5515434451219512</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5515434451219512</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.5515434451219512</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="n">
+        <v>4.585193452380953</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.672247023809524</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.320684523809524</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AA5" s="2" t="n">
         <v>1.187902267499615</v>
       </c>
     </row>
@@ -694,17 +874,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.019631171921476</v>
+        <v>1913.378684807256</v>
       </c>
       <c r="D6" t="n">
-        <v>12.40876700238484</v>
+        <v>242.2664033798944</v>
       </c>
       <c r="E6" t="n">
-        <v>9.838109237391775</v>
+        <v>192.077370825268</v>
       </c>
       <c r="F6" t="n">
         <v>1.261295916010237</v>
@@ -713,24 +893,54 @@
         <v>0.4096608027813705</v>
       </c>
       <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.335565476190476</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10.74962797619048</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.112351190476191</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10.74962797619048</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9.484747023809524</v>
+      </c>
+      <c r="O6" t="n">
+        <v>9.428943452380953</v>
+      </c>
+      <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.5505907012195123</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5505907012195123</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.5505907012195123</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.389508928571429</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.335565476190476</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.4543681355299977</v>
+      <c r="AA6" s="2" t="n">
+        <v>0.4543681355299976</v>
       </c>
     </row>
     <row r="7">
@@ -741,43 +951,70 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.046995835812017</v>
+        <v>1923.809523809524</v>
       </c>
       <c r="D7" t="n">
-        <v>12.35161709494707</v>
+        <v>241.1506194727761</v>
       </c>
       <c r="E7" t="n">
-        <v>9.858314775839085</v>
+        <v>192.4718599092393</v>
       </c>
       <c r="F7" t="n">
         <v>1.252913644552983</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4157144978901118</v>
+        <v>0.4157144978901119</v>
       </c>
       <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.218377976190476</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10.61383928571428</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.878348214285714</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10.61383928571428</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9.187127976190476</v>
+      </c>
+      <c r="O7" t="n">
+        <v>9.086681547619047</v>
+      </c>
+      <c r="P7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.5436356707317074</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.5436356707317074</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.5436356707317074</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="Q7" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.218377976190476</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.75</v>
+      <c r="AA7" s="2" t="n">
+        <v>4.65</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1025,70 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.066627007733493</v>
+        <v>1931.292517006803</v>
       </c>
       <c r="D8" t="n">
-        <v>12.24221998307763</v>
+        <v>239.0147710981823</v>
       </c>
       <c r="E8" t="n">
-        <v>9.907095263643964</v>
+        <v>193.4242408616202</v>
       </c>
       <c r="F8" t="n">
         <v>1.235702257553015</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4248234088863401</v>
+        <v>0.42482340888634</v>
       </c>
       <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.175595238095238</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10.38318452380952</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.671875000000002</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10.38318452380952</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9.014136904761905</v>
+      </c>
+      <c r="O8" t="n">
+        <v>8.976934523809524</v>
+      </c>
+      <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.5318216463414634</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.5318216463414634</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.5318216463414634</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.175595238095238</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.5505208333333333</v>
+      <c r="AA8" s="2" t="n">
+        <v>2.637369791666667</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1099,70 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.092801903628793</v>
+        <v>1941.269841269841</v>
       </c>
       <c r="D9" t="n">
-        <v>11.97811200851347</v>
+        <v>233.8583773090726</v>
       </c>
       <c r="E9" t="n">
-        <v>9.927300796276185</v>
+        <v>193.8187298320589</v>
       </c>
       <c r="F9" t="n">
         <v>1.206582962914407</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4460565364445848</v>
+        <v>0.4460565364445847</v>
       </c>
       <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9486607142857142</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.511904761904762</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8.941592261904761</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8.859747023809524</v>
+      </c>
+      <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.5121951219512195</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.5121951219512195</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5121951219512195</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="Q9" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.9486607142857142</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.5505208333333333</v>
+      <c r="AA9" s="2" t="n">
+        <v>10.306640625</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1173,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.104699583581202</v>
+        <v>1945.804988662131</v>
       </c>
       <c r="D10" t="n">
-        <v>11.62481249251017</v>
+        <v>226.9606248537699</v>
       </c>
       <c r="E10" t="n">
-        <v>9.927300804998817</v>
+        <v>193.8187300023578</v>
       </c>
       <c r="F10" t="n">
         <v>1.170994283426627</v>
@@ -901,15 +1192,48 @@
         <v>0.4746878760600517</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.02157738095238</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.264229910714286</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.02157738095238</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.740699404761905</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7.961309523809524</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.5505208333333333</v>
+      <c r="AA10" s="2" t="n">
+        <v>6.968508184523809</v>
       </c>
     </row>
     <row r="11">
@@ -920,26 +1244,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.10202260559191</v>
+        <v>1944.784580498866</v>
       </c>
       <c r="D11" t="n">
-        <v>11.52970284368934</v>
+        <v>225.1037221863156</v>
       </c>
       <c r="E11" t="n">
-        <v>9.872602253425413</v>
+        <v>192.7508059002104</v>
       </c>
       <c r="F11" t="n">
         <v>1.167848409945714</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4822986140229914</v>
+        <v>0.4822986140229912</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.565848214285714</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.073567708333333</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8.565848214285714</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.424479166666666</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7.494419642857142</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="12">
@@ -950,17 +1315,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.074063057703748</v>
+        <v>1934.126984126984</v>
       </c>
       <c r="D12" t="n">
-        <v>11.41540308696468</v>
+        <v>222.8721555074056</v>
       </c>
       <c r="E12" t="n">
-        <v>9.933218880397519</v>
+        <v>193.9342733791896</v>
       </c>
       <c r="F12" t="n">
         <v>1.149214894427842</v>
@@ -969,7 +1334,48 @@
         <v>0.4893090196273585</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8.543526785714285</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.147507440476189</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8.543526785714285</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8.39657738095238</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8.316592261904761</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>10.306640625</v>
       </c>
     </row>
     <row r="13">
@@ -980,26 +1386,67 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.058893515764426</v>
+        <v>1928.344671201814</v>
       </c>
       <c r="D13" t="n">
-        <v>11.38927945858095</v>
+        <v>222.3621227627709</v>
       </c>
       <c r="E13" t="n">
-        <v>9.961793821032455</v>
+        <v>194.4921650773003</v>
       </c>
       <c r="F13" t="n">
-        <v>1.143296043181964</v>
+        <v>1.143296043181965</v>
       </c>
       <c r="G13" t="n">
         <v>0.490086684895249</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9.136904761904761</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.246558779761904</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9.136904761904761</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8.428199404761905</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8.087797619047619</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>9.161086309523808</v>
       </c>
     </row>
     <row r="14">
@@ -1010,26 +1457,67 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.032421177870315</v>
+        <v>1918.253968253968</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36662257589945</v>
+        <v>221.919774100894</v>
       </c>
       <c r="E14" t="n">
-        <v>10.03077985309973</v>
+        <v>195.8390352271852</v>
       </c>
       <c r="F14" t="n">
         <v>1.133174363545314</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4894676189081906</v>
+        <v>0.4894676189081907</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9.640997023809524</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7.449776785714285</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9.640997023809524</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8.335193452380953</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8.013392857142856</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>9.239676339285714</v>
       </c>
     </row>
     <row r="15">
@@ -1040,35 +1528,67 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.001487209994051</v>
+        <v>1906.462585034014</v>
       </c>
       <c r="D15" t="n">
-        <v>11.25722547275264</v>
+        <v>219.7839258965992</v>
       </c>
       <c r="E15" t="n">
-        <v>10.02241043346684</v>
+        <v>195.6756322724478</v>
       </c>
       <c r="F15" t="n">
-        <v>1.123205395297173</v>
+        <v>1.123205395297174</v>
       </c>
       <c r="G15" t="n">
         <v>0.4959595954863608</v>
       </c>
       <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9.990699404761903</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.440941220238095</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.51171875</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.51171875</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.51171875</v>
+      <c r="M15" t="n">
+        <v>9.990699404761903</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>8.045014880952381</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7.918526785714286</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -1079,17 +1599,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.966983938132064</v>
+        <v>1893.310657596372</v>
       </c>
       <c r="D16" t="n">
-        <v>11.3464170345446</v>
+        <v>221.5252849601564</v>
       </c>
       <c r="E16" t="n">
-        <v>10.0224104305593</v>
+        <v>195.6756322156815</v>
       </c>
       <c r="F16" t="n">
         <v>1.13210460828348</v>
@@ -1098,16 +1618,48 @@
         <v>0.4848251447903331</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5343940548780488</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5343940548780488</v>
+        <v>10.43340773809524</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5343940548780488</v>
+        <v>7.61532738095238</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>10.43340773809524</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8.324032738095237</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7.894345238095237</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>6.559709821428571</v>
       </c>
     </row>
     <row r="17">
@@ -1118,17 +1670,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.875371802498513</v>
+        <v>1858.390022675737</v>
       </c>
       <c r="D17" t="n">
-        <v>11.32621146702185</v>
+        <v>221.1307953085218</v>
       </c>
       <c r="E17" t="n">
-        <v>9.939136912183065</v>
+        <v>194.0498159045265</v>
       </c>
       <c r="F17" t="n">
         <v>1.13955684151393</v>
@@ -1137,16 +1689,48 @@
         <v>0.4775823557220801</v>
       </c>
       <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11.13653273809524</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7.578124999999999</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.5704077743902439</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.5704077743902439</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.5704077743902439</v>
+      <c r="M17" t="n">
+        <v>11.13653273809524</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8.106398809523808</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7.736235119047619</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="n">
+        <v>6.964595734126983</v>
       </c>
     </row>
     <row r="18">
@@ -1157,17 +1741,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.817370612730517</v>
+        <v>1836.281179138322</v>
       </c>
       <c r="D18" t="n">
-        <v>11.32029342651367</v>
+        <v>221.015252612886</v>
       </c>
       <c r="E18" t="n">
-        <v>9.91056196573304</v>
+        <v>193.4919240928832</v>
       </c>
       <c r="F18" t="n">
         <v>1.142245360621824</v>
@@ -1176,16 +1760,48 @@
         <v>0.4723941979211876</v>
       </c>
       <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10.83519345238095</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.44931175595238</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.5549733231707318</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.5549733231707318</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.5549733231707318</v>
+      <c r="M18" t="n">
+        <v>10.83519345238095</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7.974330357142857</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7.65438988095238</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="n">
+        <v>3.523809523809523</v>
       </c>
     </row>
     <row r="19">
@@ -1196,17 +1812,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.75639500297442</v>
+        <v>1813.038548752834</v>
       </c>
       <c r="D19" t="n">
-        <v>11.2488560560273</v>
+        <v>219.6205229986282</v>
       </c>
       <c r="E19" t="n">
-        <v>9.784426066933609</v>
+        <v>191.0292708306085</v>
       </c>
       <c r="F19" t="n">
         <v>1.149669482816444</v>
@@ -1215,16 +1831,48 @@
         <v>0.4723577653013291</v>
       </c>
       <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J19" t="n">
+        <v>11.16629464285714</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.442336309523808</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.5719321646341463</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.5719321646341463</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.5719321646341463</v>
+      <c r="M19" t="n">
+        <v>11.16629464285714</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7.765997023809524</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7.503720238095237</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="20">
@@ -1235,17 +1883,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.685306365258775</v>
+        <v>1785.9410430839</v>
       </c>
       <c r="D20" t="n">
-        <v>11.20252691827169</v>
+        <v>218.7160017376854</v>
       </c>
       <c r="E20" t="n">
-        <v>9.735645567498556</v>
+        <v>190.0768896511623</v>
       </c>
       <c r="F20" t="n">
         <v>1.150671194899511</v>
@@ -1254,16 +1902,48 @@
         <v>0.4691544778018248</v>
       </c>
       <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="J20" t="n">
+        <v>11.15513392857143</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.379557291666667</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.571360518292683</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.571360518292683</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.571360518292683</v>
+      <c r="M20" t="n">
+        <v>11.15513392857143</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7.513020833333333</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7.040550595238095</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="n">
+        <v>1.417643229166667</v>
       </c>
     </row>
     <row r="21">
@@ -1274,17 +1954,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.504759071980964</v>
+        <v>1717.120181405896</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07393965197773</v>
+        <v>216.2054884433746</v>
       </c>
       <c r="E21" t="n">
-        <v>9.601140263603956</v>
+        <v>187.450833717982</v>
       </c>
       <c r="F21" t="n">
         <v>1.15339838268553</v>
@@ -1293,16 +1973,48 @@
         <v>0.4616120398506867</v>
       </c>
       <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10.69754464285714</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.975446428571428</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.547923018292683</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.547923018292683</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.547923018292683</v>
+      <c r="M21" t="n">
+        <v>10.69754464285714</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7.204241071428571</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6.666666666666666</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="n">
+        <v>1.404761904761905</v>
       </c>
     </row>
     <row r="22">
@@ -1312,7 +2024,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1335,6 +2055,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/26/Filled_2D_sections/coronal/week26_coronal_Batch_Allmarks.xlsx
+++ b/measurements/26/Filled_2D_sections/coronal/week26_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2092,4 +2298,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week26_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1889.365079365079</v>
+      </c>
+      <c r="D10" t="n">
+        <v>59.70903160408278</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1717.120181405896</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1945.804988662131</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>229.0530590925898</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.971202440744699</v>
+      </c>
+      <c r="E11" t="n">
+        <v>216.2054884433746</v>
+      </c>
+      <c r="F11" t="n">
+        <v>242.7764352730342</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.187902267499616</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05473657308279628</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.123205395297174</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.265789516022532</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4543681355299976</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03414680265353116</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.403711103559776</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4959595954863608</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0109.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0110.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0111.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0112.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0113.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0115.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0116.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0117.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0118.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0119.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0121.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0122.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0123.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0125.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.8750939799154207</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.967906041546987</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.967906041546987</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.8750939799154205</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>38</v>
+      </c>
+      <c r="C48" t="n">
+        <v>9.780554902882207</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.8823412087467306</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.324032738095237</v>
+      </c>
+      <c r="F48" t="n">
+        <v>11.56808035714286</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>42</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.952558106575963</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.063965137992773</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8.428199404761905</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>13</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.412688873626374</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.2245775881874814</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9486607142857142</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.791294642857143</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>